--- a/CLP03N.xlsx
+++ b/CLP03N.xlsx
@@ -11,21 +11,642 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="272">
   <si>
     <t/>
   </si>
   <si>
+    <t>20114582</t>
+  </si>
+  <si>
+    <t>KMBO PROBITES ORG 60</t>
+  </si>
+  <si>
+    <t>CLP03N</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-7H)</t>
+  </si>
+  <si>
+    <t>20114657</t>
+  </si>
+  <si>
+    <t>KMBO PRBTE KOREAN 60</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20129115</t>
+  </si>
+  <si>
+    <t>KMBO PRBTS AM/CHS 50</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20139292</t>
+  </si>
+  <si>
+    <t>KMBO BASO SWT&amp;SPC 60</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>20139812</t>
+  </si>
+  <si>
+    <t>MABELL GOCHUJANG 60G</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20139811</t>
+  </si>
+  <si>
+    <t>MABELL SS S.TEMPONG</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20138744</t>
+  </si>
+  <si>
+    <t>ROYAL SS DAEGU 55G</t>
+  </si>
+  <si>
+    <t>20138743</t>
+  </si>
+  <si>
+    <t>ROYAL SS JEJU 55G</t>
+  </si>
+  <si>
+    <t>20138745</t>
+  </si>
+  <si>
+    <t>ROYAL SS NAMI 55G</t>
+  </si>
+  <si>
+    <t>20137694</t>
+  </si>
+  <si>
+    <t>SOSIS EAT ORIGINL 65</t>
+  </si>
+  <si>
+    <t>20137693</t>
+  </si>
+  <si>
+    <t>SOSIS EAT PEDAS 65G</t>
+  </si>
+  <si>
+    <t>20137695</t>
+  </si>
+  <si>
+    <t>SOSIS EAT KEJU 65G</t>
+  </si>
+  <si>
+    <t>20140289</t>
+  </si>
+  <si>
+    <t>EOMUK BAR KOREAN 65G</t>
+  </si>
+  <si>
+    <t>20140288</t>
+  </si>
+  <si>
+    <t>EOMUK BAR CHEESE 65G</t>
+  </si>
+  <si>
+    <t>20138974</t>
+  </si>
+  <si>
+    <t>FIESTA RTG BRATWURST</t>
+  </si>
+  <si>
+    <t>20134963</t>
+  </si>
+  <si>
+    <t>FIESTA SSG RTG CHS65</t>
+  </si>
+  <si>
+    <t>20132114</t>
+  </si>
+  <si>
+    <t>FIESTA BKSO AY BBQ60</t>
+  </si>
+  <si>
+    <t>20132113</t>
+  </si>
+  <si>
+    <t>FIESTA BKSO AYM KJ60</t>
+  </si>
+  <si>
+    <t>20132112</t>
+  </si>
+  <si>
+    <t>FIESTA SMY AYM RTG54</t>
+  </si>
+  <si>
+    <t>20138476</t>
+  </si>
+  <si>
+    <t>FIESTA S.RTG H.BBQ60</t>
+  </si>
+  <si>
+    <t>20140367</t>
+  </si>
+  <si>
+    <t>FIESTA SS MENTAI 60G</t>
+  </si>
+  <si>
+    <t>20139683</t>
+  </si>
+  <si>
+    <t>FIESTA RTG H.LAVA 60</t>
+  </si>
+  <si>
+    <t>20139682</t>
+  </si>
+  <si>
+    <t>FIESTA RTG C.LAVA 60</t>
+  </si>
+  <si>
+    <t>20139684</t>
+  </si>
+  <si>
+    <t>FIESTA BAKSO MN.LAVA</t>
+  </si>
+  <si>
+    <t>20138976</t>
+  </si>
+  <si>
+    <t>FIESTA BAKSO CH.LV55</t>
+  </si>
+  <si>
+    <t>20137459</t>
+  </si>
+  <si>
+    <t>KZLR BAKSO GCHJNG 55</t>
+  </si>
+  <si>
+    <t>20127239</t>
+  </si>
+  <si>
+    <t>KANZLR BAKSO HOT 55G</t>
+  </si>
+  <si>
+    <t>20118404</t>
+  </si>
+  <si>
+    <t>KANZLR BAKSO KJU 48G</t>
+  </si>
+  <si>
+    <t>20118403</t>
+  </si>
+  <si>
+    <t>KANZLR BAKSO ORI 48G</t>
+  </si>
+  <si>
+    <t>20135147</t>
+  </si>
+  <si>
+    <t>FIESTA SSG RTG KRN60</t>
+  </si>
+  <si>
+    <t>20128986</t>
+  </si>
+  <si>
+    <t>FIESTA SSG RTG ORI65</t>
+  </si>
+  <si>
+    <t>20126489</t>
+  </si>
+  <si>
+    <t>KNZLER SNGL GCHJNG60</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20106308</t>
+  </si>
+  <si>
+    <t>KNZLER SNGLES HOT 65</t>
+  </si>
+  <si>
+    <t>20141057</t>
+  </si>
+  <si>
+    <t>KZLER SS TOM YUM 60G</t>
+  </si>
+  <si>
+    <t>20088730</t>
+  </si>
+  <si>
+    <t>KNZLER SNGLES KJU 60</t>
+  </si>
+  <si>
+    <t>20088719</t>
+  </si>
+  <si>
+    <t>KNZLER SNGLES ORG 65</t>
+  </si>
+  <si>
+    <t>20088731</t>
+  </si>
+  <si>
+    <t>KNZLER SNGLES MN 65</t>
+  </si>
+  <si>
+    <t>20140035</t>
+  </si>
+  <si>
+    <t>CIMORY THICK ORNG 40</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20140036</t>
+  </si>
+  <si>
+    <t>CIMORY THICK GRPE 40</t>
+  </si>
+  <si>
+    <t>20129787</t>
+  </si>
+  <si>
+    <t>CMORY YOG.T&amp;C STRW40</t>
+  </si>
+  <si>
+    <t>20133604</t>
+  </si>
+  <si>
+    <t>CMORY YOG.T&amp;C ORIG40</t>
+  </si>
+  <si>
+    <t>20134040</t>
+  </si>
+  <si>
+    <t>CMORY YOG.T&amp;C MNGO40</t>
+  </si>
+  <si>
+    <t>20131933</t>
+  </si>
+  <si>
+    <t>CMORY YOG.T&amp;C BLUE40</t>
+  </si>
+  <si>
+    <t>20139288</t>
+  </si>
+  <si>
+    <t>LARISST COCOPANDN360</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139289</t>
+  </si>
+  <si>
+    <t>LARISST VANILLA 360G</t>
+  </si>
+  <si>
+    <t>20084429</t>
+  </si>
+  <si>
+    <t>KIN YOGURT ORGNL 200</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20084430</t>
+  </si>
+  <si>
+    <t>KIN YOGURT SRTW 200</t>
+  </si>
+  <si>
+    <t>20090512</t>
+  </si>
+  <si>
+    <t>KIN YOGURT BLUBR 200</t>
+  </si>
+  <si>
+    <t>20117940</t>
+  </si>
+  <si>
+    <t>KIN B/YOGRT BLCK 200</t>
+  </si>
+  <si>
+    <t>20133220</t>
+  </si>
+  <si>
+    <t>KIN B/YOG MANG-GO200</t>
+  </si>
+  <si>
+    <t>20095318</t>
+  </si>
+  <si>
+    <t>GRNFIELDS YOG BLU240</t>
+  </si>
+  <si>
+    <t>20095317</t>
+  </si>
+  <si>
+    <t>GRNFIELDS YOG STR240</t>
+  </si>
+  <si>
+    <t>20140123</t>
+  </si>
+  <si>
+    <t>CIMORY STRAWBRY 240</t>
+  </si>
+  <si>
+    <t>20140122</t>
+  </si>
+  <si>
+    <t>CIMORY BLUEBERRY 240</t>
+  </si>
+  <si>
+    <t>20140171</t>
+  </si>
+  <si>
+    <t>CIMORY TR.FRUIT 240</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20023797</t>
+  </si>
+  <si>
+    <t>CIMORY YOGHRT MIX240</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20131858</t>
+  </si>
+  <si>
+    <t>BIOKUL YOG STRWBRY80</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20131857</t>
+  </si>
+  <si>
+    <t>BIOKUL YOG LYCHEE 80</t>
+  </si>
+  <si>
+    <t>20139813</t>
+  </si>
+  <si>
+    <t>BIOKUL MRSHMALLOW 80</t>
+  </si>
+  <si>
+    <t>20139859</t>
+  </si>
+  <si>
+    <t>BIOKUL BROWN SGR 80</t>
+  </si>
+  <si>
+    <t>20139814</t>
+  </si>
+  <si>
+    <t>BIOKUL TO GO YUZU 80</t>
+  </si>
+  <si>
+    <t>20028005</t>
+  </si>
+  <si>
+    <t>CIMORY YGRT BLBRY240</t>
+  </si>
+  <si>
+    <t>20015231</t>
+  </si>
+  <si>
+    <t>CIMORY YOGHRT STR240</t>
+  </si>
+  <si>
+    <t>20052812</t>
+  </si>
+  <si>
+    <t>CIMORY MIX BERRY 240</t>
+  </si>
+  <si>
+    <t>20103269</t>
+  </si>
+  <si>
+    <t>CMORY NO ADD ST&amp;M240</t>
+  </si>
+  <si>
+    <t>20099974</t>
+  </si>
+  <si>
+    <t>WG COCO CCPNDAN 220G</t>
+  </si>
+  <si>
+    <t>20106309</t>
+  </si>
+  <si>
+    <t>W/COCO DUGAN CPND220</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20141580</t>
+  </si>
+  <si>
+    <t>KIN YGR SLURP ORIG80</t>
+  </si>
+  <si>
+    <t>RT,(E-15H)</t>
+  </si>
+  <si>
+    <t>20141581</t>
+  </si>
+  <si>
+    <t>KIN YGR SLURP SLAD80</t>
+  </si>
+  <si>
+    <t>20136640</t>
+  </si>
+  <si>
+    <t>KIN YGR SLURP MGO 80</t>
+  </si>
+  <si>
+    <t>20136637</t>
+  </si>
+  <si>
+    <t>KIN YGR SLURP BLU 80</t>
+  </si>
+  <si>
+    <t>20136638</t>
+  </si>
+  <si>
+    <t>KIN YGR SLURP STR 80</t>
+  </si>
+  <si>
+    <t>20103575</t>
+  </si>
+  <si>
+    <t>IDM NATA DCS STR 200</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20103576</t>
+  </si>
+  <si>
+    <t>IDM NATA DC LYCH 200</t>
+  </si>
+  <si>
+    <t>10015550</t>
+  </si>
+  <si>
+    <t>P/R FRUIT COCKTL.220</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>RT,(E-30H)</t>
+  </si>
+  <si>
+    <t>20047616</t>
+  </si>
+  <si>
+    <t>W/COCO PUDD MNGO 120</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20047617</t>
+  </si>
+  <si>
+    <t>W/COCO PUDD GUAV 120</t>
+  </si>
+  <si>
+    <t>20129570</t>
+  </si>
+  <si>
+    <t>W/COCO PUD BLBRY 120</t>
+  </si>
+  <si>
+    <t>20065442</t>
+  </si>
+  <si>
+    <t>HB GREEK YGR STW 100</t>
+  </si>
+  <si>
+    <t>RT,(E-2H)</t>
+  </si>
+  <si>
+    <t>20065444</t>
+  </si>
+  <si>
+    <t>HB GREEK YGR PEC 100</t>
+  </si>
+  <si>
+    <t>20127008</t>
+  </si>
+  <si>
+    <t>YOSEO COKIES CREAM90</t>
+  </si>
+  <si>
+    <t>20127011</t>
+  </si>
+  <si>
+    <t>YOSEO CHESCAK STR110</t>
+  </si>
+  <si>
+    <t>20119852</t>
+  </si>
+  <si>
+    <t>HB GREEK YGR STRW200</t>
+  </si>
+  <si>
+    <t>20077454</t>
+  </si>
+  <si>
+    <t>HB GREEK YGR CLS 200</t>
+  </si>
+  <si>
+    <t>20124744</t>
+  </si>
+  <si>
+    <t>S/N SS PRMIUM ORI 60</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20124746</t>
+  </si>
+  <si>
+    <t>S/N SS PRM SMK/BRT60</t>
+  </si>
+  <si>
+    <t>20137392</t>
+  </si>
+  <si>
+    <t>SG SOSIS JPG KEJU 55</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20137391</t>
+  </si>
+  <si>
+    <t>SG SOSIS JPG HOT 55G</t>
+  </si>
+  <si>
+    <t>20140885</t>
+  </si>
+  <si>
+    <t>SG KOREA CHS BLDK 58</t>
+  </si>
+  <si>
+    <t>20140884</t>
+  </si>
+  <si>
+    <t>SG KOREA BULDAK 58G</t>
+  </si>
+  <si>
+    <t>20132652</t>
+  </si>
+  <si>
+    <t>S/N SS PRM HOT 55G</t>
+  </si>
+  <si>
+    <t>20124745</t>
+  </si>
+  <si>
+    <t>S/N SS PRMIUM KEJU60</t>
+  </si>
+  <si>
     <t>10038137</t>
   </si>
   <si>
     <t>YAKULT FRMNTASI 5X65</t>
   </si>
   <si>
-    <t>CLP03N</t>
-  </si>
-  <si>
-    <t>1</t>
+    <t>15</t>
   </si>
   <si>
     <t>RT,(E-3H)</t>
@@ -37,73 +658,25 @@
     <t>YAKULT LGHT L/S 5X65</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-7H)</t>
-  </si>
-  <si>
     <t>20138478</t>
   </si>
   <si>
     <t>YAKULT MANGGA 5X65ML</t>
   </si>
   <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>TG,(E-3H)</t>
   </si>
   <si>
-    <t>20131858</t>
-  </si>
-  <si>
-    <t>BIOKUL YOG STRWBRY80</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20131857</t>
-  </si>
-  <si>
-    <t>BIOKUL YOG LYCHEE 80</t>
-  </si>
-  <si>
-    <t>20136640</t>
-  </si>
-  <si>
-    <t>KIN YGR SLURP MGO 80</t>
-  </si>
-  <si>
-    <t>RT,(E-15H)</t>
-  </si>
-  <si>
-    <t>20136637</t>
-  </si>
-  <si>
-    <t>KIN YGR SLURP BLU 80</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20136638</t>
-  </si>
-  <si>
-    <t>KIN YGR SLURP STR 80</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>20137599</t>
   </si>
   <si>
     <t>IDMLK YGRT BN.BRS 70</t>
   </si>
   <si>
-    <t>6</t>
+    <t>17</t>
   </si>
   <si>
     <t>20137601</t>
@@ -112,25 +685,130 @@
     <t>IDMLK YOGRT STRAW 70</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>20137602</t>
   </si>
   <si>
     <t>IDMLK YGRT BLUBRY 70</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>20137603</t>
   </si>
   <si>
     <t>IDMLK YOGRT ORI 70G</t>
   </si>
   <si>
-    <t>9</t>
+    <t>20119841</t>
+  </si>
+  <si>
+    <t>GRNFIELDS YOG STR110</t>
+  </si>
+  <si>
+    <t>20119874</t>
+  </si>
+  <si>
+    <t>GRNFIELDS YOG BLU110</t>
+  </si>
+  <si>
+    <t>20119844</t>
+  </si>
+  <si>
+    <t>GRNFIELDS YOG MNG110</t>
+  </si>
+  <si>
+    <t>20118503</t>
+  </si>
+  <si>
+    <t>CIMORY SQZ MANGO 120</t>
+  </si>
+  <si>
+    <t>20122460</t>
+  </si>
+  <si>
+    <t>CMORY SQZ BR/SGR 120</t>
+  </si>
+  <si>
+    <t>20135436</t>
+  </si>
+  <si>
+    <t>CMORY BITE STR.MG120</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20135255</t>
+  </si>
+  <si>
+    <t>CMORY BITE BLBRY120</t>
+  </si>
+  <si>
+    <t>20135437</t>
+  </si>
+  <si>
+    <t>CMORY BITE BERRY120</t>
+  </si>
+  <si>
+    <t>20135254</t>
+  </si>
+  <si>
+    <t>CMORY BITES STRAW120</t>
+  </si>
+  <si>
+    <t>20135336</t>
+  </si>
+  <si>
+    <t>CMORY BITE STR LC120</t>
+  </si>
+  <si>
+    <t>20141571</t>
+  </si>
+  <si>
+    <t>CMORY ALMND&amp;DATE 120</t>
+  </si>
+  <si>
+    <t>20102569</t>
+  </si>
+  <si>
+    <t>CMORY SQZE BLUBR 120</t>
+  </si>
+  <si>
+    <t>20102567</t>
+  </si>
+  <si>
+    <t>CIMORY SQZE STRW 120</t>
+  </si>
+  <si>
+    <t>20102570</t>
+  </si>
+  <si>
+    <t>CIMORY SQZE ORGN 120</t>
+  </si>
+  <si>
+    <t>20138151</t>
+  </si>
+  <si>
+    <t>CMORY EAT MLK MRIE80</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20138147</t>
+  </si>
+  <si>
+    <t>CMORY EAT MLK HZL 80</t>
+  </si>
+  <si>
+    <t>20138150</t>
+  </si>
+  <si>
+    <t>CMORY EAT MLK CHO 80</t>
+  </si>
+  <si>
+    <t>20141051</t>
+  </si>
+  <si>
+    <t>CMRY EAT MILK MATCHA</t>
   </si>
   <si>
     <t>20141328</t>
@@ -149,678 +827,6 @@
   </si>
   <si>
     <t>G/F FRS MLK F/CRM320</t>
-  </si>
-  <si>
-    <t>20119841</t>
-  </si>
-  <si>
-    <t>GRNFIELDS YOG STR110</t>
-  </si>
-  <si>
-    <t>20119844</t>
-  </si>
-  <si>
-    <t>GRNFIELDS YOG MNG110</t>
-  </si>
-  <si>
-    <t>20119874</t>
-  </si>
-  <si>
-    <t>GRNFIELDS YOG BLU110</t>
-  </si>
-  <si>
-    <t>20139288</t>
-  </si>
-  <si>
-    <t>LARISST COCOPANDN360</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139289</t>
-  </si>
-  <si>
-    <t>LARISST VANILLA 360G</t>
-  </si>
-  <si>
-    <t>20139813</t>
-  </si>
-  <si>
-    <t>BIOKUL MRSHMALLOW 80</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20139859</t>
-  </si>
-  <si>
-    <t>BIOKUL BROWN SGR 80</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20139814</t>
-  </si>
-  <si>
-    <t>BIOKUL TO GO YUZU 80</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>10015550</t>
-  </si>
-  <si>
-    <t>P/R FRUIT COCKTL.220</t>
-  </si>
-  <si>
-    <t>RT,(E-30H)</t>
-  </si>
-  <si>
-    <t>20106309</t>
-  </si>
-  <si>
-    <t>W/COCO DUGAN CPND220</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20099974</t>
-  </si>
-  <si>
-    <t>WG COCO CCPNDAN 220G</t>
-  </si>
-  <si>
-    <t>20129570</t>
-  </si>
-  <si>
-    <t>W/COCO PUD BLBRY 120</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20047617</t>
-  </si>
-  <si>
-    <t>W/COCO PUDD GUAV 120</t>
-  </si>
-  <si>
-    <t>20103575</t>
-  </si>
-  <si>
-    <t>IDM NATA DCS STR 200</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20103576</t>
-  </si>
-  <si>
-    <t>IDM NATA DC LYCH 200</t>
-  </si>
-  <si>
-    <t>20047616</t>
-  </si>
-  <si>
-    <t>W/COCO PUDD MNGO 120</t>
-  </si>
-  <si>
-    <t>20119852</t>
-  </si>
-  <si>
-    <t>HB GREEK YGR STRW200</t>
-  </si>
-  <si>
-    <t>20077454</t>
-  </si>
-  <si>
-    <t>HB GREEK YGR CLS 200</t>
-  </si>
-  <si>
-    <t>20138744</t>
-  </si>
-  <si>
-    <t>ROYAL SS DAEGU 55G</t>
-  </si>
-  <si>
-    <t>20138745</t>
-  </si>
-  <si>
-    <t>ROYAL SS NAMI 55G</t>
-  </si>
-  <si>
-    <t>20138743</t>
-  </si>
-  <si>
-    <t>ROYAL SS JEJU 55G</t>
-  </si>
-  <si>
-    <t>20140289</t>
-  </si>
-  <si>
-    <t>EOMUK BAR KOREAN 65G</t>
-  </si>
-  <si>
-    <t>20140288</t>
-  </si>
-  <si>
-    <t>EOMUK BAR CHEESE 65G</t>
-  </si>
-  <si>
-    <t>20140035</t>
-  </si>
-  <si>
-    <t>CIMORY THICK ORNG 40</t>
-  </si>
-  <si>
-    <t>20129787</t>
-  </si>
-  <si>
-    <t>CMORY YOG.T&amp;C STRW40</t>
-  </si>
-  <si>
-    <t>20140036</t>
-  </si>
-  <si>
-    <t>CIMORY THICK GRPE 40</t>
-  </si>
-  <si>
-    <t>20131933</t>
-  </si>
-  <si>
-    <t>CMORY YOG.T&amp;C BLUE40</t>
-  </si>
-  <si>
-    <t>20124746</t>
-  </si>
-  <si>
-    <t>S/N SS PRM SMK/BRT60</t>
-  </si>
-  <si>
-    <t>20141580</t>
-  </si>
-  <si>
-    <t>KIN YGR SLURP ORIG80</t>
-  </si>
-  <si>
-    <t>20124744</t>
-  </si>
-  <si>
-    <t>S/N SS PRMIUM ORI 60</t>
-  </si>
-  <si>
-    <t>20133604</t>
-  </si>
-  <si>
-    <t>CMORY YOG.T&amp;C ORIG40</t>
-  </si>
-  <si>
-    <t>20134040</t>
-  </si>
-  <si>
-    <t>CMORY YOG.T&amp;C MNGO40</t>
-  </si>
-  <si>
-    <t>20084429</t>
-  </si>
-  <si>
-    <t>KIN YOGURT ORGNL 200</t>
-  </si>
-  <si>
-    <t>20084430</t>
-  </si>
-  <si>
-    <t>KIN YOGURT SRTW 200</t>
-  </si>
-  <si>
-    <t>20090512</t>
-  </si>
-  <si>
-    <t>KIN YOGURT BLUBR 200</t>
-  </si>
-  <si>
-    <t>20117940</t>
-  </si>
-  <si>
-    <t>KIN B/YOGRT BLCK 200</t>
-  </si>
-  <si>
-    <t>20133220</t>
-  </si>
-  <si>
-    <t>KIN B/YOG MANG-GO200</t>
-  </si>
-  <si>
-    <t>20095318</t>
-  </si>
-  <si>
-    <t>GRNFIELDS YOG BLU240</t>
-  </si>
-  <si>
-    <t>20095317</t>
-  </si>
-  <si>
-    <t>GRNFIELDS YOG STR240</t>
-  </si>
-  <si>
-    <t>20028005</t>
-  </si>
-  <si>
-    <t>CIMORY YGRT BLBRY240</t>
-  </si>
-  <si>
-    <t>20015231</t>
-  </si>
-  <si>
-    <t>CIMORY YOGHRT STR240</t>
-  </si>
-  <si>
-    <t>20052812</t>
-  </si>
-  <si>
-    <t>CIMORY MIX BERRY 240</t>
-  </si>
-  <si>
-    <t>20103269</t>
-  </si>
-  <si>
-    <t>CMORY NO ADD ST&amp;M240</t>
-  </si>
-  <si>
-    <t>20023797</t>
-  </si>
-  <si>
-    <t>CIMORY YOGHRT MIX240</t>
-  </si>
-  <si>
-    <t>20140123</t>
-  </si>
-  <si>
-    <t>CIMORY STRAWBRY 240</t>
-  </si>
-  <si>
-    <t>20140122</t>
-  </si>
-  <si>
-    <t>CIMORY BLUEBERRY 240</t>
-  </si>
-  <si>
-    <t>20140171</t>
-  </si>
-  <si>
-    <t>CIMORY TR.FRUIT 240</t>
-  </si>
-  <si>
-    <t>20102569</t>
-  </si>
-  <si>
-    <t>CMORY SQZE BLUBR 120</t>
-  </si>
-  <si>
-    <t>20102567</t>
-  </si>
-  <si>
-    <t>CIMORY SQZE STRW 120</t>
-  </si>
-  <si>
-    <t>20102570</t>
-  </si>
-  <si>
-    <t>CIMORY SQZE ORGN 120</t>
-  </si>
-  <si>
-    <t>20118503</t>
-  </si>
-  <si>
-    <t>CIMORY SQZ MANGO 120</t>
-  </si>
-  <si>
-    <t>20122460</t>
-  </si>
-  <si>
-    <t>CMORY SQZ BR/SGR 120</t>
-  </si>
-  <si>
-    <t>20138151</t>
-  </si>
-  <si>
-    <t>CMORY EAT MLK MRIE80</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20138147</t>
-  </si>
-  <si>
-    <t>CMORY EAT MLK HZL 80</t>
-  </si>
-  <si>
-    <t>20138150</t>
-  </si>
-  <si>
-    <t>CMORY EAT MLK CHO 80</t>
-  </si>
-  <si>
-    <t>20141051</t>
-  </si>
-  <si>
-    <t>CMRY EAT MILK MATCHA</t>
-  </si>
-  <si>
-    <t>20135436</t>
-  </si>
-  <si>
-    <t>CMORY BITE STR.MG120</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20135255</t>
-  </si>
-  <si>
-    <t>CMORY BITE BLBRY120</t>
-  </si>
-  <si>
-    <t>20135437</t>
-  </si>
-  <si>
-    <t>CMORY BITE BERRY120</t>
-  </si>
-  <si>
-    <t>20135254</t>
-  </si>
-  <si>
-    <t>CMORY BITES STRAW120</t>
-  </si>
-  <si>
-    <t>20135336</t>
-  </si>
-  <si>
-    <t>CMORY BITE STR LC120</t>
-  </si>
-  <si>
-    <t>20141571</t>
-  </si>
-  <si>
-    <t>CMORY ALMND&amp;DATE 120</t>
-  </si>
-  <si>
-    <t>20139682</t>
-  </si>
-  <si>
-    <t>FIESTA RTG C.LAVA 60</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20139683</t>
-  </si>
-  <si>
-    <t>FIESTA RTG H.LAVA 60</t>
-  </si>
-  <si>
-    <t>20139684</t>
-  </si>
-  <si>
-    <t>FIESTA BAKSO MN.LAVA</t>
-  </si>
-  <si>
-    <t>20138974</t>
-  </si>
-  <si>
-    <t>FIESTA RTG BRATWURST</t>
-  </si>
-  <si>
-    <t>20138976</t>
-  </si>
-  <si>
-    <t>FIESTA BAKSO CH.LV55</t>
-  </si>
-  <si>
-    <t>20140367</t>
-  </si>
-  <si>
-    <t>FIESTA SS MENTAI 60G</t>
-  </si>
-  <si>
-    <t>20127008</t>
-  </si>
-  <si>
-    <t>YOSEO COKIES CREAM90</t>
-  </si>
-  <si>
-    <t>20127011</t>
-  </si>
-  <si>
-    <t>YOSEO CHESCAK STR110</t>
-  </si>
-  <si>
-    <t>20065442</t>
-  </si>
-  <si>
-    <t>HB GREEK YGR STW 100</t>
-  </si>
-  <si>
-    <t>RT,(E-2H)</t>
-  </si>
-  <si>
-    <t>20065444</t>
-  </si>
-  <si>
-    <t>HB GREEK YGR PEC 100</t>
-  </si>
-  <si>
-    <t>20114582</t>
-  </si>
-  <si>
-    <t>KMBO PROBITES ORG 60</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20139292</t>
-  </si>
-  <si>
-    <t>KMBO BASO SWT&amp;SPC 60</t>
-  </si>
-  <si>
-    <t>20114657</t>
-  </si>
-  <si>
-    <t>KMBO PRBTE KOREAN 60</t>
-  </si>
-  <si>
-    <t>20129115</t>
-  </si>
-  <si>
-    <t>KMBO PRBTS AM/CHS 50</t>
-  </si>
-  <si>
-    <t>20137694</t>
-  </si>
-  <si>
-    <t>SOSIS EAT ORIGINL 65</t>
-  </si>
-  <si>
-    <t>20137693</t>
-  </si>
-  <si>
-    <t>SOSIS EAT PEDAS 65G</t>
-  </si>
-  <si>
-    <t>20140884</t>
-  </si>
-  <si>
-    <t>SG KOREA BULDAK 58G</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20124745</t>
-  </si>
-  <si>
-    <t>S/N SS PRMIUM KEJU60</t>
-  </si>
-  <si>
-    <t>20140885</t>
-  </si>
-  <si>
-    <t>SG KOREA CHS BLDK 58</t>
-  </si>
-  <si>
-    <t>20132652</t>
-  </si>
-  <si>
-    <t>S/N SS PRM HOT 55G</t>
-  </si>
-  <si>
-    <t>20137392</t>
-  </si>
-  <si>
-    <t>SG SOSIS JPG KEJU 55</t>
-  </si>
-  <si>
-    <t>20137391</t>
-  </si>
-  <si>
-    <t>SG SOSIS JPG HOT 55G</t>
-  </si>
-  <si>
-    <t>20137695</t>
-  </si>
-  <si>
-    <t>SOSIS EAT KEJU 65G</t>
-  </si>
-  <si>
-    <t>20139812</t>
-  </si>
-  <si>
-    <t>MABELL GOCHUJANG 60G</t>
-  </si>
-  <si>
-    <t>20139811</t>
-  </si>
-  <si>
-    <t>MABELL SS S.TEMPONG</t>
-  </si>
-  <si>
-    <t>20135147</t>
-  </si>
-  <si>
-    <t>FIESTA SSG RTG KRN60</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20134963</t>
-  </si>
-  <si>
-    <t>FIESTA SSG RTG CHS65</t>
-  </si>
-  <si>
-    <t>20132112</t>
-  </si>
-  <si>
-    <t>FIESTA SMY AYM RTG54</t>
-  </si>
-  <si>
-    <t>20132114</t>
-  </si>
-  <si>
-    <t>FIESTA BKSO AY BBQ60</t>
-  </si>
-  <si>
-    <t>20138476</t>
-  </si>
-  <si>
-    <t>FIESTA S.RTG H.BBQ60</t>
-  </si>
-  <si>
-    <t>20118403</t>
-  </si>
-  <si>
-    <t>KANZLR BAKSO ORI 48G</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20118404</t>
-  </si>
-  <si>
-    <t>KANZLR BAKSO KJU 48G</t>
-  </si>
-  <si>
-    <t>20127239</t>
-  </si>
-  <si>
-    <t>KANZLR BAKSO HOT 55G</t>
-  </si>
-  <si>
-    <t>20128986</t>
-  </si>
-  <si>
-    <t>FIESTA SSG RTG ORI65</t>
-  </si>
-  <si>
-    <t>20088731</t>
-  </si>
-  <si>
-    <t>KNZLER SNGLES MN 65</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20088719</t>
-  </si>
-  <si>
-    <t>KNZLER SNGLES ORG 65</t>
-  </si>
-  <si>
-    <t>20088730</t>
-  </si>
-  <si>
-    <t>KNZLER SNGLES KJU 60</t>
-  </si>
-  <si>
-    <t>20137459</t>
-  </si>
-  <si>
-    <t>KZLR BAKSO GCHJNG 55</t>
-  </si>
-  <si>
-    <t>20106308</t>
-  </si>
-  <si>
-    <t>KNZLER SNGLES HOT 65</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20126489</t>
-  </si>
-  <si>
-    <t>KNZLER SNGL GCHJNG60</t>
-  </si>
-  <si>
-    <t>20141057</t>
-  </si>
-  <si>
-    <t>KZLER SS TOM YUM 60G</t>
   </si>
 </sst>
 </file>
@@ -1213,7 +1219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1280,264 +1286,264 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -1545,19 +1551,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1565,19 +1571,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -1585,19 +1591,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -1605,1130 +1611,1130 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>68</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>71</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>123</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>126</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>9</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>9</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>65</v>
+        <v>126</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>65</v>
+        <v>126</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>9</v>
+        <v>150</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>9</v>
+        <v>153</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>9</v>
+        <v>153</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>9</v>
+        <v>153</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>9</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>9</v>
+        <v>153</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>9</v>
+        <v>164</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>9</v>
+        <v>164</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -2737,18 +2743,18 @@
         <v>169</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>9</v>
+        <v>170</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -2757,18 +2763,18 @@
         <v>169</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>9</v>
+        <v>173</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -2777,358 +2783,358 @@
         <v>169</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>9</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>9</v>
+        <v>173</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>9</v>
+        <v>173</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>199</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>9</v>
+        <v>173</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>9</v>
+        <v>173</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3137,30 +3143,30 @@
         <v>217</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>76</v>
+        <v>218</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="C97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3174,13 +3180,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3194,13 +3200,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3214,13 +3220,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3234,13 +3240,13 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3254,13 +3260,13 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3274,13 +3280,13 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>9</v>
+        <v>212</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3294,53 +3300,53 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>238</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="C106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3354,13 +3360,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3374,13 +3380,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3394,213 +3400,253 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="E115" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B120" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>9</v>
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/CLP03N.xlsx
+++ b/CLP03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="280">
   <si>
     <t/>
   </si>
@@ -599,6 +599,30 @@
   </si>
   <si>
     <t>S/N SS PRM SMK/BRT60</t>
+  </si>
+  <si>
+    <t>20141974</t>
+  </si>
+  <si>
+    <t>SG ITALIAN TRFFLE 58</t>
+  </si>
+  <si>
+    <t>20141982</t>
+  </si>
+  <si>
+    <t>SG GRMN SMKD CHSE 60</t>
+  </si>
+  <si>
+    <t>20141983</t>
+  </si>
+  <si>
+    <t>SG FRNCH LMON SS 58G</t>
+  </si>
+  <si>
+    <t>20141984</t>
+  </si>
+  <si>
+    <t>SG KOREA GCHJANG 55G</t>
   </si>
   <si>
     <t>20137392</t>
@@ -1219,7 +1243,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2980,10 +3004,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -2991,19 +3015,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3011,19 +3035,19 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3031,19 +3055,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3051,22 +3075,22 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>173</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3080,13 +3104,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>173</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3100,30 +3124,30 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>212</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3131,79 +3155,79 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>218</v>
+        <v>173</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>5</v>
+        <v>173</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>220</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>5</v>
@@ -3211,42 +3235,42 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>212</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3260,13 +3284,13 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>212</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3280,13 +3304,13 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>212</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3300,10 +3324,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>5</v>
@@ -3320,13 +3344,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>220</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3340,50 +3364,50 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>220</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>220</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3391,19 +3415,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3411,19 +3435,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3440,10 +3464,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3460,10 +3484,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3480,10 +3504,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3500,10 +3524,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3520,10 +3544,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3531,19 +3555,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3551,19 +3575,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>86</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3571,19 +3595,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3591,19 +3615,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3620,10 +3644,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3640,13 +3664,93 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="E121" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E125" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F121" s="1" t="s">
-        <v>212</v>
+      <c r="F125" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/CLP03N.xlsx
+++ b/CLP03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="278">
   <si>
     <t/>
   </si>
@@ -572,12 +572,6 @@
   </si>
   <si>
     <t>YOSEO CHESCAK STR110</t>
-  </si>
-  <si>
-    <t>20119852</t>
-  </si>
-  <si>
-    <t>HB GREEK YGR STRW200</t>
   </si>
   <si>
     <t>20077454</t>
@@ -1243,7 +1237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2927,7 +2921,7 @@
         <v>169</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -2944,30 +2938,30 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>5</v>
+        <v>173</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>173</v>
@@ -2984,13 +2978,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>173</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3004,10 +2998,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3024,10 +3018,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3044,10 +3038,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3064,10 +3058,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3075,19 +3069,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>5</v>
@@ -3104,10 +3098,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3124,10 +3118,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3144,13 +3138,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>5</v>
+        <v>173</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3164,10 +3158,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>173</v>
@@ -3184,33 +3178,33 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>173</v>
+        <v>218</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B98" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>220</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3224,50 +3218,50 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>5</v>
+        <v>224</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>226</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3284,10 +3278,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3304,10 +3298,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>5</v>
@@ -3324,13 +3318,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>5</v>
+        <v>218</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3344,13 +3338,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3364,13 +3358,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3384,13 +3378,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>220</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3404,10 +3398,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -3424,10 +3418,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3435,19 +3429,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3464,10 +3458,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3484,10 +3478,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>5</v>
@@ -3504,10 +3498,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3524,10 +3518,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>5</v>
@@ -3544,10 +3538,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3564,10 +3558,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3584,10 +3578,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3604,10 +3598,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3615,19 +3609,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>5</v>
@@ -3644,10 +3638,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3664,10 +3658,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3684,10 +3678,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3704,10 +3698,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>5</v>
@@ -3724,33 +3718,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/CLP03N.xlsx
+++ b/CLP03N.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="272">
   <si>
     <t/>
   </si>
   <si>
-    <t>20114582</t>
-  </si>
-  <si>
-    <t>KMBO PROBITES ORG 60</t>
+    <t>20139812</t>
+  </si>
+  <si>
+    <t>MABELL GOCHUJANG 60G</t>
   </si>
   <si>
     <t>CLP03N</t>
@@ -28,70 +28,64 @@
     <t>1</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>RT,(E-7H)</t>
   </si>
   <si>
-    <t>20114657</t>
-  </si>
-  <si>
-    <t>KMBO PRBTE KOREAN 60</t>
+    <t>20139811</t>
+  </si>
+  <si>
+    <t>MABELL SS S.TEMPONG</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20138744</t>
+  </si>
+  <si>
+    <t>ROYAL SS DAEGU 55G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20129115</t>
-  </si>
-  <si>
-    <t>KMBO PRBTS AM/CHS 50</t>
+    <t>20138743</t>
+  </si>
+  <si>
+    <t>ROYAL SS JEJU 55G</t>
+  </si>
+  <si>
+    <t>20138745</t>
+  </si>
+  <si>
+    <t>ROYAL SS NAMI 55G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20139292</t>
-  </si>
-  <si>
-    <t>KMBO BASO SWT&amp;SPC 60</t>
+    <t>20142305</t>
+  </si>
+  <si>
+    <t>BF QUICK BIT CRAB 60</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20139812</t>
-  </si>
-  <si>
-    <t>MABELL GOCHUJANG 60G</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>20139811</t>
-  </si>
-  <si>
-    <t>MABELL SS S.TEMPONG</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20138744</t>
-  </si>
-  <si>
-    <t>ROYAL SS DAEGU 55G</t>
-  </si>
-  <si>
-    <t>20138743</t>
-  </si>
-  <si>
-    <t>ROYAL SS JEJU 55G</t>
-  </si>
-  <si>
-    <t>20138745</t>
-  </si>
-  <si>
-    <t>ROYAL SS NAMI 55G</t>
+    <t>20142306</t>
+  </si>
+  <si>
+    <t>BF QUICK BIT F/TOF60</t>
+  </si>
+  <si>
+    <t>20142304</t>
+  </si>
+  <si>
+    <t>BF QUICK BIT ODENG60</t>
   </si>
   <si>
     <t>20137694</t>
@@ -130,6 +124,9 @@
     <t>FIESTA RTG BRATWURST</t>
   </si>
   <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
     <t>20134963</t>
   </si>
   <si>
@@ -497,21 +494,6 @@
   </si>
   <si>
     <t>KIN YGR SLURP STR 80</t>
-  </si>
-  <si>
-    <t>20103575</t>
-  </si>
-  <si>
-    <t>IDM NATA DCS STR 200</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20103576</t>
-  </si>
-  <si>
-    <t>IDM NATA DC LYCH 200</t>
   </si>
   <si>
     <t>10015550</t>
@@ -1237,7 +1219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1281,18 +1263,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -1301,50 +1283,50 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1358,13 +1340,13 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1378,13 +1360,13 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1398,13 +1380,13 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1418,13 +1400,13 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1438,13 +1420,13 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1458,13 +1440,13 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1478,13 +1460,13 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1498,13 +1480,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1518,13 +1500,13 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1538,1313 +1520,1313 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="E33" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>86</v>
+        <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>99</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="E47" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>99</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>126</v>
+        <v>4</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>5</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>99</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>5</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="E74" s="1" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>173</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>180</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2858,13 +2840,13 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>180</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2878,73 +2860,73 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>5</v>
+        <v>167</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="E83" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>5</v>
+        <v>167</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>173</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2958,13 +2940,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>173</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -2978,13 +2960,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -2998,73 +2980,73 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="E89" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3078,13 +3060,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>167</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3098,13 +3080,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>167</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3118,133 +3100,133 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>5</v>
+        <v>212</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B95" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="E95" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>173</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>173</v>
+        <v>218</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>218</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>224</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3258,13 +3240,13 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>5</v>
+        <v>212</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3278,13 +3260,13 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>212</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3298,13 +3280,13 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>5</v>
+        <v>212</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3318,13 +3300,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>218</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3338,13 +3320,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>218</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3358,73 +3340,73 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>218</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3438,13 +3420,13 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3458,13 +3440,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3478,13 +3460,13 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3498,13 +3480,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3518,13 +3500,13 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3538,73 +3520,73 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3618,13 +3600,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3638,13 +3620,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3658,73 +3640,13 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/CLP03N.xlsx
+++ b/CLP03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="274">
   <si>
     <t/>
   </si>
@@ -446,6 +446,12 @@
   </si>
   <si>
     <t>CMORY NO ADD ST&amp;M240</t>
+  </si>
+  <si>
+    <t>20030414</t>
+  </si>
+  <si>
+    <t>CIMORY YGRT LYCHE240</t>
   </si>
   <si>
     <t>20099974</t>
@@ -1219,7 +1225,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2540,10 +2546,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>4</v>
+        <v>122</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -2563,18 +2569,18 @@
         <v>125</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>149</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2583,18 +2589,18 @@
         <v>125</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -2603,10 +2609,10 @@
         <v>125</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2623,10 +2629,10 @@
         <v>125</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2643,10 +2649,10 @@
         <v>125</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2663,10 +2669,10 @@
         <v>125</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2680,53 +2686,53 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="E74" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2740,13 +2746,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2760,33 +2766,33 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>176</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2800,13 +2806,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>6</v>
+        <v>176</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2820,7 +2826,7 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>5</v>
@@ -2840,10 +2846,10 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>6</v>
@@ -2860,33 +2866,33 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>167</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="C83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="E83" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2900,13 +2906,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2920,10 +2926,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>6</v>
@@ -2940,10 +2946,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>6</v>
@@ -2960,10 +2966,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>6</v>
@@ -2980,10 +2986,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>6</v>
@@ -2991,19 +2997,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="E89" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>6</v>
@@ -3020,10 +3026,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>6</v>
@@ -3040,10 +3046,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>6</v>
@@ -3060,13 +3066,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>167</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3080,13 +3086,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3100,33 +3106,33 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>212</v>
+        <v>169</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="E95" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3140,50 +3146,50 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>218</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>221</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>6</v>
+        <v>220</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>6</v>
@@ -3200,10 +3206,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>6</v>
@@ -3220,10 +3226,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>6</v>
@@ -3240,13 +3246,13 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>212</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3260,13 +3266,13 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3280,13 +3286,13 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3300,13 +3306,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>6</v>
+        <v>214</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3320,10 +3326,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>6</v>
@@ -3340,10 +3346,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>103</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>6</v>
@@ -3351,19 +3357,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="E107" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>6</v>
@@ -3380,10 +3386,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>6</v>
@@ -3400,10 +3406,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>6</v>
@@ -3420,10 +3426,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>6</v>
@@ -3440,10 +3446,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>6</v>
@@ -3460,10 +3466,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>6</v>
@@ -3480,10 +3486,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>6</v>
@@ -3500,10 +3506,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>6</v>
@@ -3520,10 +3526,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>103</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>6</v>
@@ -3531,19 +3537,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>6</v>
@@ -3560,10 +3566,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>6</v>
@@ -3580,10 +3586,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>6</v>
@@ -3600,10 +3606,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>6</v>
@@ -3620,10 +3626,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>6</v>
@@ -3640,13 +3646,33 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E121" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E122" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F121" s="1" t="s">
-        <v>212</v>
+      <c r="F122" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/CLP03N.xlsx
+++ b/CLP03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="280">
   <si>
     <t/>
   </si>
@@ -118,6 +118,21 @@
     <t>EOMUK BAR CHEESE 65G</t>
   </si>
   <si>
+    <t>20142574</t>
+  </si>
+  <si>
+    <t>CEDEA CHIKUWA B/P50G</t>
+  </si>
+  <si>
+    <t>20142575</t>
+  </si>
+  <si>
+    <t>CEDEA CRB STIK SPC50</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>20138974</t>
   </si>
   <si>
@@ -229,9 +244,6 @@
     <t>KNZLER SNGL GCHJNG60</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>20106308</t>
   </si>
   <si>
@@ -674,6 +686,12 @@
   </si>
   <si>
     <t>TG,(E-3H)</t>
+  </si>
+  <si>
+    <t>20142608</t>
+  </si>
+  <si>
+    <t>YAKULT STRWBR 5X65ML</t>
   </si>
   <si>
     <t>20137599</t>
@@ -1225,7 +1243,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F122"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1526,33 +1544,33 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1569,18 +1587,18 @@
         <v>20</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1589,18 +1607,18 @@
         <v>20</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1609,58 +1627,58 @@
         <v>20</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F21" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1669,18 +1687,18 @@
         <v>5</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1689,18 +1707,18 @@
         <v>5</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1709,18 +1727,18 @@
         <v>5</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1729,58 +1747,58 @@
         <v>5</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F27" s="1" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1789,7 +1807,7 @@
         <v>9</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>6</v>
@@ -1797,10 +1815,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1809,7 +1827,7 @@
         <v>9</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>6</v>
@@ -1817,10 +1835,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1829,18 +1847,18 @@
         <v>9</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1849,30 +1867,30 @@
         <v>9</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1886,13 +1904,13 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1906,10 +1924,10 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>6</v>
@@ -1926,10 +1944,10 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>6</v>
@@ -1946,10 +1964,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>6</v>
@@ -1966,10 +1984,10 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>6</v>
@@ -1986,10 +2004,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -1997,19 +2015,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>6</v>
@@ -2017,19 +2035,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="E40" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>6</v>
@@ -2046,10 +2064,10 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>6</v>
@@ -2066,10 +2084,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -2086,10 +2104,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>6</v>
@@ -2106,90 +2124,90 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>98</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>98</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="C46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>6</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="E48" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>6</v>
@@ -2206,13 +2224,13 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>98</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2226,13 +2244,13 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>98</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2246,13 +2264,13 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>6</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2266,13 +2284,13 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>6</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2286,10 +2304,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>6</v>
@@ -2306,10 +2324,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -2326,10 +2344,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>6</v>
@@ -2337,19 +2355,19 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -2357,62 +2375,62 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F57" s="1" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F58" s="1" t="s">
-        <v>128</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="C59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2426,13 +2444,13 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2446,13 +2464,13 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2466,13 +2484,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>6</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2486,13 +2504,13 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>6</v>
+        <v>102</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2506,10 +2524,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>6</v>
@@ -2526,10 +2544,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>6</v>
@@ -2546,10 +2564,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>122</v>
+        <v>89</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -2566,10 +2584,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>6</v>
@@ -2586,73 +2604,73 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>12</v>
+        <v>126</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>151</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>154</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2666,13 +2684,13 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2686,13 +2704,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2706,73 +2724,73 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2786,53 +2804,53 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>178</v>
-      </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="C80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2846,13 +2864,13 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>6</v>
+        <v>180</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2866,10 +2884,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>6</v>
@@ -2886,53 +2904,53 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="E85" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>6</v>
+        <v>173</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2946,13 +2964,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>6</v>
+        <v>173</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -2966,10 +2984,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>6</v>
@@ -2986,10 +3004,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>6</v>
@@ -3006,10 +3024,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>6</v>
@@ -3017,19 +3035,19 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>6</v>
@@ -3037,19 +3055,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="C91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="E91" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>6</v>
@@ -3066,10 +3084,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>6</v>
@@ -3086,13 +3104,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3106,13 +3124,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3126,70 +3144,70 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>6</v>
+        <v>173</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>219</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>6</v>
@@ -3197,10 +3215,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3209,18 +3227,18 @@
         <v>223</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>6</v>
+        <v>224</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>227</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3229,27 +3247,27 @@
         <v>223</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>6</v>
+        <v>224</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>6</v>
@@ -3266,13 +3284,13 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>214</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3286,13 +3304,13 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>214</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3306,13 +3324,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>214</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3326,13 +3344,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>6</v>
+        <v>218</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3346,13 +3364,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>6</v>
+        <v>218</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3366,30 +3384,30 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>6</v>
+        <v>218</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>6</v>
@@ -3397,19 +3415,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>246</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>6</v>
@@ -3417,19 +3435,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C110" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C110" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>6</v>
@@ -3446,10 +3464,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>6</v>
@@ -3466,10 +3484,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>6</v>
@@ -3486,10 +3504,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>6</v>
@@ -3506,10 +3524,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>6</v>
@@ -3526,10 +3544,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>6</v>
@@ -3546,10 +3564,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>6</v>
@@ -3557,19 +3575,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>6</v>
@@ -3577,19 +3595,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>6</v>
@@ -3597,19 +3615,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>6</v>
@@ -3626,10 +3644,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>6</v>
@@ -3646,10 +3664,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>6</v>
@@ -3666,13 +3684,73 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>214</v>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/CLP03N.xlsx
+++ b/CLP03N.xlsx
@@ -247,13 +247,13 @@
     <t>20106308</t>
   </si>
   <si>
-    <t>KNZLER SNGLES HOT 65</t>
+    <t>KNZLER SNGL HOT 65 G</t>
   </si>
   <si>
     <t>20141057</t>
   </si>
   <si>
-    <t>KZLER SS TOM YUM 60G</t>
+    <t>KNZLER TOM YUM 60 G</t>
   </si>
   <si>
     <t>20088730</t>
@@ -265,7 +265,7 @@
     <t>20088719</t>
   </si>
   <si>
-    <t>KNZLER SNGLES ORG 65</t>
+    <t>KNZLER SNGL ORG 65 G</t>
   </si>
   <si>
     <t>20088731</t>

--- a/CLP03N.xlsx
+++ b/CLP03N.xlsx
@@ -247,13 +247,13 @@
     <t>20106308</t>
   </si>
   <si>
-    <t>KNZLER SNGL HOT 65 G</t>
+    <t>KNZLER SNGLES HOT 65</t>
   </si>
   <si>
     <t>20141057</t>
   </si>
   <si>
-    <t>KNZLER TOM YUM 60 G</t>
+    <t>KZLER SS TOM YUM 60G</t>
   </si>
   <si>
     <t>20088730</t>
@@ -265,7 +265,7 @@
     <t>20088719</t>
   </si>
   <si>
-    <t>KNZLER SNGL ORG 65 G</t>
+    <t>KNZLER SNGLES ORG 65</t>
   </si>
   <si>
     <t>20088731</t>

--- a/CLP03N.xlsx
+++ b/CLP03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="278">
   <si>
     <t/>
   </si>
@@ -782,12 +782,6 @@
   </si>
   <si>
     <t>CMORY BITE STR LC120</t>
-  </si>
-  <si>
-    <t>20141571</t>
-  </si>
-  <si>
-    <t>CMORY ALMND&amp;DATE 120</t>
   </si>
   <si>
     <t>20102569</t>
@@ -1243,7 +1237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3547,7 +3541,7 @@
         <v>248</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>6</v>
@@ -3567,7 +3561,7 @@
         <v>248</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>6</v>
@@ -3587,7 +3581,7 @@
         <v>248</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>6</v>
@@ -3604,10 +3598,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>6</v>
@@ -3615,19 +3609,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>6</v>
@@ -3644,10 +3638,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>6</v>
@@ -3664,10 +3658,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>6</v>
@@ -3684,10 +3678,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>6</v>
@@ -3704,10 +3698,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>6</v>
@@ -3724,32 +3718,12 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F125" s="1" t="s">
         <v>218</v>
       </c>
     </row>

--- a/CLP03N.xlsx
+++ b/CLP03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="280">
   <si>
     <t/>
   </si>
@@ -512,6 +512,12 @@
   </si>
   <si>
     <t>KIN YGR SLURP STR 80</t>
+  </si>
+  <si>
+    <t>20143176</t>
+  </si>
+  <si>
+    <t>KIN Y/S XL BLACK 80</t>
   </si>
   <si>
     <t>10015550</t>
@@ -1237,7 +1243,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2758,53 +2764,53 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>170</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="E77" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2818,13 +2824,13 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2838,33 +2844,33 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2878,13 +2884,13 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>6</v>
+        <v>182</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2898,7 +2904,7 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>5</v>
@@ -2918,10 +2924,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>6</v>
@@ -2938,33 +2944,33 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>173</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="E86" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -2978,13 +2984,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>6</v>
+        <v>175</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -2998,10 +3004,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>6</v>
@@ -3018,10 +3024,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>6</v>
@@ -3038,10 +3044,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>6</v>
@@ -3058,10 +3064,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>6</v>
@@ -3069,19 +3075,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C92" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="E92" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>6</v>
@@ -3098,10 +3104,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>6</v>
@@ -3118,10 +3124,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>6</v>
@@ -3138,13 +3144,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>173</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3158,13 +3164,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3178,33 +3184,33 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>218</v>
+        <v>175</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="E98" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F98" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3218,33 +3224,33 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>224</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="E100" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3258,30 +3264,30 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>6</v>
+        <v>226</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E102" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>6</v>
@@ -3298,10 +3304,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>6</v>
@@ -3318,10 +3324,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>6</v>
@@ -3338,13 +3344,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>218</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3358,13 +3364,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3378,13 +3384,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3398,13 +3404,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>6</v>
+        <v>220</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3418,10 +3424,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>6</v>
@@ -3438,10 +3444,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>6</v>
@@ -3449,19 +3455,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>6</v>
@@ -3478,10 +3484,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>6</v>
@@ -3498,10 +3504,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>6</v>
@@ -3518,10 +3524,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>6</v>
@@ -3538,10 +3544,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>6</v>
@@ -3558,10 +3564,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>6</v>
@@ -3578,10 +3584,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>6</v>
@@ -3598,10 +3604,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>6</v>
@@ -3609,19 +3615,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="C119" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="E119" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>6</v>
@@ -3638,10 +3644,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>6</v>
@@ -3658,10 +3664,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>6</v>
@@ -3678,10 +3684,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>6</v>
@@ -3698,10 +3704,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>6</v>
@@ -3718,13 +3724,33 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E124" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E125" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F124" s="1" t="s">
-        <v>218</v>
+      <c r="F125" s="1" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/CLP03N.xlsx
+++ b/CLP03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="286">
   <si>
     <t/>
   </si>
@@ -586,6 +586,18 @@
     <t>HB GREEK YGR CLS 200</t>
   </si>
   <si>
+    <t>20141325</t>
+  </si>
+  <si>
+    <t>HMTOWN HONI PNP 110G</t>
+  </si>
+  <si>
+    <t>20141326</t>
+  </si>
+  <si>
+    <t>HMETOWN MX BRIES 110</t>
+  </si>
+  <si>
     <t>20124744</t>
   </si>
   <si>
@@ -806,6 +818,12 @@
   </si>
   <si>
     <t>CIMORY SQZE ORGN 120</t>
+  </si>
+  <si>
+    <t>20143175</t>
+  </si>
+  <si>
+    <t>CMRY BLBERY CSCKE120</t>
   </si>
   <si>
     <t>20138151</t>
@@ -1243,7 +1261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2964,53 +2982,53 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>175</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>175</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="C88" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="E88" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>6</v>
+        <v>175</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3024,13 +3042,13 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>6</v>
+        <v>175</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3044,10 +3062,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>6</v>
@@ -3064,10 +3082,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>6</v>
@@ -3084,10 +3102,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>6</v>
@@ -3095,19 +3113,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>6</v>
@@ -3115,19 +3133,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="E94" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>6</v>
@@ -3144,10 +3162,10 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>6</v>
@@ -3164,13 +3182,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>175</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3184,13 +3202,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>175</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3204,130 +3222,130 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>220</v>
+        <v>175</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>6</v>
+        <v>175</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>226</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>6</v>
+        <v>230</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>233</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>6</v>
+        <v>230</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="C104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>231</v>
-      </c>
       <c r="E104" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>6</v>
@@ -3344,10 +3362,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>6</v>
@@ -3364,13 +3382,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>220</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3384,13 +3402,13 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>220</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -3404,13 +3422,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3424,13 +3442,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>6</v>
+        <v>224</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3444,13 +3462,13 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>6</v>
+        <v>224</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3464,10 +3482,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>6</v>
@@ -3475,19 +3493,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>6</v>
@@ -3495,19 +3513,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="C113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="E113" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>6</v>
@@ -3524,10 +3542,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>6</v>
@@ -3544,10 +3562,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>6</v>
@@ -3564,10 +3582,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>6</v>
@@ -3584,10 +3602,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>6</v>
@@ -3604,10 +3622,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>6</v>
@@ -3624,10 +3642,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>6</v>
@@ -3635,19 +3653,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>6</v>
@@ -3655,19 +3673,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>6</v>
@@ -3675,19 +3693,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="E122" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>6</v>
@@ -3704,10 +3722,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>6</v>
@@ -3724,10 +3742,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>6</v>
@@ -3744,13 +3762,73 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E125" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E128" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F125" s="1" t="s">
-        <v>220</v>
+      <c r="F128" s="1" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/CLP03N.xlsx
+++ b/CLP03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="287">
   <si>
     <t/>
   </si>
@@ -88,6 +88,15 @@
     <t>BF QUICK BIT ODENG60</t>
   </si>
   <si>
+    <t>20143394</t>
+  </si>
+  <si>
+    <t>BF QCKBIT SPCY BBQ50</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>20137694</t>
   </si>
   <si>
@@ -130,9 +139,6 @@
     <t>CEDEA CRB STIK SPC50</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>20138974</t>
   </si>
   <si>
@@ -701,9 +707,6 @@
   </si>
   <si>
     <t>16</t>
-  </si>
-  <si>
-    <t>TG,(E-3H)</t>
   </si>
   <si>
     <t>20142608</t>
@@ -1261,7 +1264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F128"/>
+  <dimension ref="A1:F129"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1462,10 +1465,10 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>6</v>
@@ -1473,10 +1476,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -1485,7 +1488,7 @@
         <v>17</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>6</v>
@@ -1493,10 +1496,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1505,7 +1508,7 @@
         <v>17</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>6</v>
@@ -1513,10 +1516,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1525,7 +1528,7 @@
         <v>17</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>6</v>
@@ -1533,10 +1536,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1545,7 +1548,7 @@
         <v>17</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>6</v>
@@ -1553,10 +1556,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1565,7 +1568,7 @@
         <v>17</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>6</v>
@@ -1573,10 +1576,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1585,7 +1588,7 @@
         <v>17</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>6</v>
@@ -1602,21 +1605,21 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1625,10 +1628,10 @@
         <v>20</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1645,10 +1648,10 @@
         <v>20</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1665,10 +1668,10 @@
         <v>20</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1685,10 +1688,10 @@
         <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1702,13 +1705,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F22" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1725,10 +1728,10 @@
         <v>5</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1745,10 +1748,10 @@
         <v>5</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1765,10 +1768,10 @@
         <v>5</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1785,10 +1788,10 @@
         <v>5</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1805,10 +1808,10 @@
         <v>5</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1822,13 +1825,13 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1845,7 +1848,7 @@
         <v>9</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>6</v>
@@ -1865,7 +1868,7 @@
         <v>9</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>6</v>
@@ -1885,7 +1888,7 @@
         <v>9</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>6</v>
@@ -1905,10 +1908,10 @@
         <v>9</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1925,10 +1928,10 @@
         <v>9</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1942,13 +1945,13 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1962,10 +1965,10 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>6</v>
@@ -1982,10 +1985,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>6</v>
@@ -2002,10 +2005,10 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>6</v>
@@ -2022,10 +2025,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -2042,10 +2045,10 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>6</v>
@@ -2062,10 +2065,10 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>6</v>
@@ -2073,19 +2076,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="E41" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>6</v>
@@ -2102,10 +2105,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -2122,10 +2125,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>6</v>
@@ -2142,10 +2145,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -2162,10 +2165,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -2182,33 +2185,33 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="C47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2222,30 +2225,30 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>6</v>
+        <v>104</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="E49" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>6</v>
@@ -2262,10 +2265,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -2282,13 +2285,13 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2302,13 +2305,13 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2322,13 +2325,13 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>6</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2342,10 +2345,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -2362,10 +2365,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>6</v>
@@ -2382,10 +2385,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -2402,10 +2405,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>6</v>
@@ -2413,19 +2416,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>6</v>
@@ -2433,42 +2436,42 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="C59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F59" s="1" t="s">
-        <v>132</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2482,13 +2485,13 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -2502,13 +2505,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2522,13 +2525,13 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2542,13 +2545,13 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>6</v>
+        <v>104</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2562,10 +2565,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>6</v>
@@ -2582,10 +2585,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -2602,10 +2605,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>6</v>
@@ -2622,10 +2625,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>6</v>
@@ -2642,10 +2645,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>6</v>
@@ -2662,53 +2665,53 @@
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>155</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="C71" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2722,13 +2725,13 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2742,13 +2745,13 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -2762,13 +2765,13 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -2782,13 +2785,13 @@
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>6</v>
+        <v>160</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -2802,53 +2805,53 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>172</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="E78" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>174</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2862,13 +2865,13 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2882,33 +2885,33 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>20</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2922,13 +2925,13 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>6</v>
+        <v>184</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2942,7 +2945,7 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>5</v>
@@ -2962,10 +2965,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>6</v>
@@ -2982,10 +2985,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>6</v>
@@ -3002,10 +3005,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>6</v>
@@ -3022,33 +3025,33 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>4</v>
+        <v>109</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>175</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="E89" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3062,13 +3065,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>6</v>
+        <v>177</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3082,10 +3085,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>6</v>
@@ -3102,10 +3105,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>6</v>
@@ -3122,10 +3125,10 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>6</v>
@@ -3142,10 +3145,10 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>6</v>
@@ -3153,19 +3156,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="E95" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>6</v>
@@ -3182,10 +3185,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>6</v>
@@ -3202,10 +3205,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>6</v>
@@ -3222,13 +3225,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>175</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3242,13 +3245,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3262,33 +3265,33 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>224</v>
+        <v>177</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="E101" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3302,70 +3305,70 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>230</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>6</v>
+        <v>226</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>235</v>
-      </c>
       <c r="E105" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>6</v>
@@ -3373,19 +3376,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>239</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>6</v>
@@ -3393,19 +3396,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>6</v>
@@ -3413,99 +3416,99 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>224</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>249</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>6</v>
+        <v>226</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>6</v>
@@ -3513,19 +3516,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>4</v>
+        <v>109</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>6</v>
@@ -3533,19 +3536,19 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="E114" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>6</v>
@@ -3553,19 +3556,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>6</v>
@@ -3573,19 +3576,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>6</v>
@@ -3593,19 +3596,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>262</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>6</v>
@@ -3613,19 +3616,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>264</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>6</v>
@@ -3633,19 +3636,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>6</v>
@@ -3653,19 +3656,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>268</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>6</v>
@@ -3673,19 +3676,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>270</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>6</v>
@@ -3693,19 +3696,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>272</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>4</v>
+        <v>128</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>6</v>
@@ -3713,19 +3716,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="E123" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>6</v>
@@ -3733,19 +3736,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>6</v>
@@ -3753,19 +3756,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>6</v>
@@ -3773,19 +3776,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>6</v>
@@ -3793,19 +3796,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>6</v>
@@ -3813,22 +3816,42 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>224</v>
+      <c r="B129" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/CLP03N.xlsx
+++ b/CLP03N.xlsx
@@ -247,25 +247,25 @@
     <t>20126489</t>
   </si>
   <si>
-    <t>KNZLER SNGL GCHJNG60</t>
+    <t>KNZLR SNGL GJNG 60 G</t>
   </si>
   <si>
     <t>20106308</t>
   </si>
   <si>
-    <t>KNZLER SNGLES HOT 65</t>
+    <t>KNZLR SNGL HOT 65 G</t>
   </si>
   <si>
     <t>20141057</t>
   </si>
   <si>
-    <t>KZLER SS TOM YUM 60G</t>
+    <t>KNZLR S TOM YUM 60 G</t>
   </si>
   <si>
     <t>20088730</t>
   </si>
   <si>
-    <t>KNZLER SNGLES KJU 60</t>
+    <t>KNZLR SNGL KEJU 60 G</t>
   </si>
   <si>
     <t>20088719</t>
